--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-hb.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-hb.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294" uniqueCount="604">
   <si>
     <t>Property</t>
   </si>
@@ -1887,9 +1887,6 @@
   </si>
   <si>
     <t>Observation.component.value[x].unit</t>
-  </si>
-  <si>
-    <t>L</t>
   </si>
   <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.system</t>
@@ -15026,7 +15023,7 @@
         <v>81</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>597</v>
+        <v>410</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>81</v>
@@ -15097,10 +15094,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15214,10 +15211,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15262,7 +15259,7 @@
         <v>81</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>597</v>
+        <v>410</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>81</v>
@@ -15333,7 +15330,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>565</v>
@@ -15452,7 +15449,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>569</v>
@@ -15571,7 +15568,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>572</v>
